--- a/Employee_Reports_wi52/Jeffrey Sayson Bagatua Q0536.xlsx
+++ b/Employee_Reports_wi52/Jeffrey Sayson Bagatua Q0536.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-13</v>
+        <v>-21</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
